--- a/outputs/master-plan/Master Plan.xlsx
+++ b/outputs/master-plan/Master Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\PtrPMDV\outputs\master-plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C91297C-8DC7-48EC-BE01-B58F9896F31B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F90CF5B6-A881-4513-8AA4-F6BF776072E8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,12 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="479">
   <si>
     <t>MASTER PLAN - FOOD DELIVERY MANAGEMENT SYSTEM</t>
   </si>
   <si>
-    <t>Kế hoạch triển khai bám theo food_delivery_db.sql và yêu cầu bài tập lớn | Cập nhật: 26/09/2026</t>
+    <t>Kế hoạch triển khai bám theo food_delivery_db.sql và yêu cầu bài tập lớn | Cập nhật: 27/09/2026</t>
   </si>
   <si>
     <t>Tiến độ công việc</t>
@@ -47,7 +47,7 @@
     <t>Mốc hiện tại</t>
   </si>
   <si>
-    <t>3.5/20</t>
+    <t>4.8/20</t>
   </si>
   <si>
     <t>Phạm vi và tiến độ thực tế</t>
@@ -74,13 +74,13 @@
     <t>Đã triển khai</t>
   </si>
   <si>
-    <t>API foundation, auth/RBAC, restaurant/menu, catalog search, promotion/favorites, cart/checkout, restaurant order state machine, notification and test workflow 2.2-3.5</t>
+    <t>API foundation, auth/RBAC, restaurant/menu, catalog search, promotion/favorites, cart/checkout, restaurant order state machine; đã bổ sung shipper, delivery/GPS, payment/COD, invoice, chat/support/review, refund/wallet và settlement 4.1-4.8</t>
   </si>
   <si>
     <t>Còn xác nhận</t>
   </si>
   <si>
-    <t>Còn xác nhận: MySQL end-to-end trên môi trường triển khai, Redis/realtime/GPS, Docker/CI và các nhóm 4.x trở đi</t>
+    <t>Còn xác nhận: realtime WebSocket/Redis hoàn chỉnh, Docker/CI, OpenAPI/Postman đầy đủ, test E2E triển khai và dữ liệu thật do người dùng nhập sau</t>
   </si>
   <si>
     <t>Tiến độ theo nhóm công việc</t>
@@ -557,7 +557,7 @@
     <t>HTML, JavaScript, Tailwind CSS + design tokens dùng chung</t>
   </si>
   <si>
-    <t>Đã có UI ordering/catalog/checkout cho customer, queue xử lý đơn cho restaurant và design tokens dùng chung</t>
+    <t>Đã có web động gọi API thật cho 4 vai trò: Customer, Restaurant, Shipper, Admin; UI đăng nhập phân quyền, catalog/checkout, order queue, shipper delivery/earnings, ví và quản lý tài khoản</t>
   </si>
   <si>
     <t>Auth</t>
@@ -863,6 +863,9 @@
     <t>Hồ sơ và trạng thái shipper</t>
   </si>
   <si>
+    <t>Shipper profile, trạng thái nhận đơn, assignment offer/accept/reject và phân quyền shipper.</t>
+  </si>
+  <si>
     <t>shipper_documents</t>
   </si>
   <si>
@@ -932,6 +935,9 @@
     <t>Thông tin chuyến giao</t>
   </si>
   <si>
+    <t>Delivery lifecycle, delivery status history, khu vực giao hàng và cập nhật trạng thái lấy hàng/đang giao/đã giao.</t>
+  </si>
+  <si>
     <t>delivery_status_history</t>
   </si>
   <si>
@@ -947,6 +953,9 @@
     <t>4.2, 4.3</t>
   </si>
   <si>
+    <t>Delivery lifecycle, delivery status history, khu vực giao hàng và cập nhật trạng thái lấy hàng/đang giao/đã giao.; API nhận GPS shipper, lưu vị trí và phục vụ màn hình theo dõi giao hàng.</t>
+  </si>
+  <si>
     <t>delivery_assignments</t>
   </si>
   <si>
@@ -956,6 +965,9 @@
     <t>4.1, 4.2</t>
   </si>
   <si>
+    <t>Shipper profile, trạng thái nhận đơn, assignment offer/accept/reject và phân quyền shipper.; Delivery lifecycle, delivery status history, khu vực giao hàng và cập nhật trạng thái lấy hàng/đang giao/đã giao.</t>
+  </si>
+  <si>
     <t>Payment &amp; invoice</t>
   </si>
   <si>
@@ -965,6 +977,9 @@
     <t>Thanh toán của đơn</t>
   </si>
   <si>
+    <t>Payment/COD flow, giao dịch thanh toán, trạng thái thu hộ và xử lý hủy đơn liên quan thanh toán.</t>
+  </si>
+  <si>
     <t>payment_transactions</t>
   </si>
   <si>
@@ -983,6 +998,9 @@
     <t>Hóa đơn</t>
   </si>
   <si>
+    <t>Invoice/tra cứu chi tiết đơn dùng snapshot đơn hàng và dữ liệu thanh toán.</t>
+  </si>
+  <si>
     <t>Promotion &amp; engagement</t>
   </si>
   <si>
@@ -1007,6 +1025,9 @@
     <t>Đánh giá nhà hàng</t>
   </si>
   <si>
+    <t>Notification, chat theo đơn, support ticket và review nhà hàng/shipper.</t>
+  </si>
+  <si>
     <t>shipper_reviews</t>
   </si>
   <si>
@@ -1079,6 +1100,9 @@
     <t>Hủy đơn và lý do</t>
   </si>
   <si>
+    <t>Order cancellation, refund, ví khách hàng và wallet transaction.</t>
+  </si>
+  <si>
     <t>refunds</t>
   </si>
   <si>
@@ -1107,6 +1131,9 @@
   </si>
   <si>
     <t>Thu nhập shipper</t>
+  </si>
+  <si>
+    <t>Shipper earnings/withdrawals, restaurant settlement/commission và báo cáo đối soát.</t>
   </si>
   <si>
     <t>shipper_withdrawals</t>
@@ -1443,7 +1470,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1500,8 +1527,20 @@
       <color theme="1"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calitor"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1572,6 +1611,11 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1752,10 +1796,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1955,6 +2000,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1970,10 +2029,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2005,14 +2060,9 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="7">
@@ -2170,7 +2220,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -2192,7 +2242,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-87A3-41E8-AA37-3D93ED4E54DA}"/>
+              <c16:uniqueId val="{00000000-288D-4649-BED8-5B6600167ADB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2561,193 +2611,193 @@
   <dimension ref="A1:Q34"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="10" width="14" customWidth="1"/>
-    <col min="11" max="17" width="12" customWidth="1"/>
+    <col min="1" max="1" width="20" style="67" customWidth="1"/>
+    <col min="2" max="2" width="15" style="67" customWidth="1"/>
+    <col min="3" max="10" width="14" style="67" customWidth="1"/>
+    <col min="11" max="17" width="12" style="67" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="34" customHeight="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
-      <c r="O1" s="71"/>
-      <c r="P1" s="71"/>
-      <c r="Q1" s="71"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="77"/>
+      <c r="Q1" s="77"/>
     </row>
     <row r="2" spans="1:17" ht="14.5" customHeight="1">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
-      <c r="N2" s="71"/>
-      <c r="O2" s="71"/>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="71"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="74" t="s">
+      <c r="A4" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="75"/>
-      <c r="C4" s="74" t="s">
+      <c r="B4" s="72"/>
+      <c r="C4" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="75"/>
-      <c r="E4" s="74" t="s">
+      <c r="D4" s="72"/>
+      <c r="E4" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="75"/>
-      <c r="G4" s="74" t="s">
+      <c r="F4" s="72"/>
+      <c r="G4" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="75"/>
-      <c r="I4" s="74" t="s">
+      <c r="H4" s="72"/>
+      <c r="I4" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="75"/>
+      <c r="J4" s="72"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="77">
+      <c r="A5" s="81">
         <f>AVERAGE(Plan!G5:G11,Plan!G13:G19,Plan!G21:G25,Plan!G28:G35,Plan!G38:G40,Plan!G42:G44,Plan!G46:G48,Plan!G50:G54,Plan!G56:G58)</f>
-        <v>0.43181818181818182</v>
-      </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="72">
+        <v>0.61363636363636365</v>
+      </c>
+      <c r="B5" s="75"/>
+      <c r="C5" s="78">
         <f>COUNTIF(Plan!F5:F11,"Đã hoàn thành")+COUNTIF(Plan!F13:F19,"Đã hoàn thành")+COUNTIF(Plan!F21:F25,"Đã hoàn thành")+COUNTIF(Plan!F28:F35,"Đã hoàn thành")+COUNTIF(Plan!F38:F40,"Đã hoàn thành")+COUNTIF(Plan!F42:F44,"Đã hoàn thành")+COUNTIF(Plan!F46:F48,"Đã hoàn thành")+COUNTIF(Plan!F50:F54,"Đã hoàn thành")+COUNTIF(Plan!F56:F58,"Đã hoàn thành")</f>
-        <v>19</v>
-      </c>
-      <c r="D5" s="69"/>
-      <c r="E5" s="72">
+        <v>27</v>
+      </c>
+      <c r="D5" s="75"/>
+      <c r="E5" s="78">
         <f>COUNTIF(Plan!F5:F11,"Đang thực hiện")+COUNTIF(Plan!F13:F19,"Đang thực hiện")+COUNTIF(Plan!F21:F25,"Đang thực hiện")+COUNTIF(Plan!F28:F35,"Đang thực hiện")+COUNTIF(Plan!F38:F40,"Đang thực hiện")+COUNTIF(Plan!F42:F44,"Đang thực hiện")+COUNTIF(Plan!F46:F48,"Đang thực hiện")+COUNTIF(Plan!F50:F54,"Đang thực hiện")+COUNTIF(Plan!F56:F58,"Đang thực hiện")</f>
         <v>0</v>
       </c>
-      <c r="F5" s="69"/>
-      <c r="G5" s="72">
+      <c r="F5" s="75"/>
+      <c r="G5" s="78">
         <f>COUNTIF(Plan!F5:F11,"Chưa thực hiện")+COUNTIF(Plan!F13:F19,"Chưa thực hiện")+COUNTIF(Plan!F21:F25,"Chưa thực hiện")+COUNTIF(Plan!F28:F35,"Chưa thực hiện")+COUNTIF(Plan!F38:F40,"Chưa thực hiện")+COUNTIF(Plan!F42:F44,"Chưa thực hiện")+COUNTIF(Plan!F46:F48,"Chưa thực hiện")+COUNTIF(Plan!F50:F54,"Chưa thực hiện")+COUNTIF(Plan!F56:F58,"Chưa thực hiện")</f>
-        <v>25</v>
-      </c>
-      <c r="H5" s="69"/>
-      <c r="I5" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="75"/>
+      <c r="I5" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="69"/>
+      <c r="J5" s="75"/>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="76" t="s">
+      <c r="A7" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="71"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="77"/>
     </row>
     <row r="8" spans="1:17" ht="27" customHeight="1">
       <c r="A8" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="67" t="s">
+      <c r="B8" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="69"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="74"/>
+      <c r="H8" s="75"/>
     </row>
     <row r="9" spans="1:17" ht="27" customHeight="1">
       <c r="A9" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="69"/>
+      <c r="C9" s="74"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="74"/>
+      <c r="H9" s="75"/>
     </row>
     <row r="10" spans="1:17" ht="27" customHeight="1">
       <c r="A10" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="69"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="75"/>
     </row>
     <row r="11" spans="1:17" ht="27" customHeight="1">
       <c r="A11" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="68"/>
-      <c r="H11" s="69"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="74"/>
+      <c r="H11" s="75"/>
     </row>
     <row r="12" spans="1:17" ht="27" customHeight="1">
       <c r="A12" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="68"/>
-      <c r="D12" s="68"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="68"/>
-      <c r="G12" s="68"/>
-      <c r="H12" s="69"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="75"/>
     </row>
     <row r="15" spans="1:17">
-      <c r="A15" s="81" t="s">
+      <c r="A15" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="71"/>
-      <c r="C15" s="71"/>
-      <c r="D15" s="71"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="62" t="s">
@@ -2790,7 +2840,7 @@
       </c>
       <c r="B20" s="63">
         <f>Plan!G27</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2839,51 +2889,45 @@
       </c>
     </row>
     <row r="33" spans="1:17" ht="30" customHeight="1">
-      <c r="A33" s="80"/>
-      <c r="B33" s="71"/>
-      <c r="C33" s="71"/>
-      <c r="D33" s="71"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="71"/>
-      <c r="H33" s="71"/>
-      <c r="I33" s="71"/>
-      <c r="J33" s="71"/>
-      <c r="K33" s="71"/>
-      <c r="L33" s="71"/>
-      <c r="M33" s="71"/>
-      <c r="N33" s="71"/>
-      <c r="O33" s="71"/>
-      <c r="P33" s="71"/>
-      <c r="Q33" s="71"/>
+      <c r="A33" s="84"/>
+      <c r="B33" s="77"/>
+      <c r="C33" s="77"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
+      <c r="I33" s="77"/>
+      <c r="J33" s="77"/>
+      <c r="K33" s="77"/>
+      <c r="L33" s="77"/>
+      <c r="M33" s="77"/>
+      <c r="N33" s="77"/>
+      <c r="O33" s="77"/>
+      <c r="P33" s="77"/>
+      <c r="Q33" s="77"/>
     </row>
     <row r="34" spans="1:17" ht="30" customHeight="1">
-      <c r="A34" s="70"/>
-      <c r="B34" s="71"/>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
-      <c r="I34" s="71"/>
-      <c r="J34" s="71"/>
-      <c r="K34" s="71"/>
-      <c r="L34" s="71"/>
-      <c r="M34" s="71"/>
-      <c r="N34" s="71"/>
-      <c r="O34" s="71"/>
-      <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
+      <c r="A34" s="76"/>
+      <c r="B34" s="77"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="77"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
+      <c r="I34" s="77"/>
+      <c r="J34" s="77"/>
+      <c r="K34" s="77"/>
+      <c r="L34" s="77"/>
+      <c r="M34" s="77"/>
+      <c r="N34" s="77"/>
+      <c r="O34" s="77"/>
+      <c r="P34" s="77"/>
+      <c r="Q34" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B9:H9"/>
     <mergeCell ref="A34:Q34"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
@@ -2899,6 +2943,12 @@
     <mergeCell ref="B11:H11"/>
     <mergeCell ref="A33:Q33"/>
     <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B9:H9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -2911,14 +2961,14 @@
   <dimension ref="A1:BR58"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="54" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="70" width="3.1640625" customWidth="1"/>
+    <col min="1" max="1" width="7" style="67" customWidth="1"/>
+    <col min="2" max="2" width="54" style="67" customWidth="1"/>
+    <col min="3" max="3" width="18" style="67" customWidth="1"/>
+    <col min="4" max="4" width="15" style="67" customWidth="1"/>
+    <col min="5" max="5" width="14" style="67" customWidth="1"/>
+    <col min="6" max="6" width="18" style="67" customWidth="1"/>
+    <col min="7" max="7" width="15" style="67" customWidth="1"/>
+    <col min="8" max="70" width="3.1640625" style="67" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:70" ht="28" customHeight="1">
@@ -2943,75 +2993,75 @@
       <c r="G1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="82" t="s">
+      <c r="H1" s="86" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="83"/>
-      <c r="T1" s="83"/>
-      <c r="U1" s="83"/>
-      <c r="V1" s="83"/>
-      <c r="W1" s="83"/>
-      <c r="X1" s="83"/>
-      <c r="Y1" s="83"/>
-      <c r="Z1" s="83"/>
-      <c r="AA1" s="83"/>
-      <c r="AB1" s="75"/>
-      <c r="AC1" s="84" t="s">
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
+      <c r="K1" s="87"/>
+      <c r="L1" s="87"/>
+      <c r="M1" s="87"/>
+      <c r="N1" s="87"/>
+      <c r="O1" s="87"/>
+      <c r="P1" s="87"/>
+      <c r="Q1" s="87"/>
+      <c r="R1" s="87"/>
+      <c r="S1" s="87"/>
+      <c r="T1" s="87"/>
+      <c r="U1" s="87"/>
+      <c r="V1" s="87"/>
+      <c r="W1" s="87"/>
+      <c r="X1" s="87"/>
+      <c r="Y1" s="87"/>
+      <c r="Z1" s="87"/>
+      <c r="AA1" s="87"/>
+      <c r="AB1" s="72"/>
+      <c r="AC1" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="AD1" s="83"/>
-      <c r="AE1" s="83"/>
-      <c r="AF1" s="83"/>
-      <c r="AG1" s="83"/>
-      <c r="AH1" s="83"/>
-      <c r="AI1" s="83"/>
-      <c r="AJ1" s="83"/>
-      <c r="AK1" s="83"/>
-      <c r="AL1" s="83"/>
-      <c r="AM1" s="83"/>
-      <c r="AN1" s="83"/>
-      <c r="AO1" s="83"/>
-      <c r="AP1" s="83"/>
-      <c r="AQ1" s="83"/>
-      <c r="AR1" s="83"/>
-      <c r="AS1" s="83"/>
-      <c r="AT1" s="83"/>
-      <c r="AU1" s="83"/>
-      <c r="AV1" s="83"/>
-      <c r="AW1" s="83"/>
-      <c r="AX1" s="83"/>
-      <c r="AY1" s="83"/>
-      <c r="AZ1" s="83"/>
-      <c r="BA1" s="83"/>
-      <c r="BB1" s="83"/>
-      <c r="BC1" s="83"/>
-      <c r="BD1" s="83"/>
-      <c r="BE1" s="83"/>
-      <c r="BF1" s="83"/>
-      <c r="BG1" s="75"/>
-      <c r="BH1" s="85" t="s">
+      <c r="AD1" s="87"/>
+      <c r="AE1" s="87"/>
+      <c r="AF1" s="87"/>
+      <c r="AG1" s="87"/>
+      <c r="AH1" s="87"/>
+      <c r="AI1" s="87"/>
+      <c r="AJ1" s="87"/>
+      <c r="AK1" s="87"/>
+      <c r="AL1" s="87"/>
+      <c r="AM1" s="87"/>
+      <c r="AN1" s="87"/>
+      <c r="AO1" s="87"/>
+      <c r="AP1" s="87"/>
+      <c r="AQ1" s="87"/>
+      <c r="AR1" s="87"/>
+      <c r="AS1" s="87"/>
+      <c r="AT1" s="87"/>
+      <c r="AU1" s="87"/>
+      <c r="AV1" s="87"/>
+      <c r="AW1" s="87"/>
+      <c r="AX1" s="87"/>
+      <c r="AY1" s="87"/>
+      <c r="AZ1" s="87"/>
+      <c r="BA1" s="87"/>
+      <c r="BB1" s="87"/>
+      <c r="BC1" s="87"/>
+      <c r="BD1" s="87"/>
+      <c r="BE1" s="87"/>
+      <c r="BF1" s="87"/>
+      <c r="BG1" s="72"/>
+      <c r="BH1" s="89" t="s">
         <v>40</v>
       </c>
-      <c r="BI1" s="83"/>
-      <c r="BJ1" s="83"/>
-      <c r="BK1" s="83"/>
-      <c r="BL1" s="83"/>
-      <c r="BM1" s="83"/>
-      <c r="BN1" s="83"/>
-      <c r="BO1" s="83"/>
-      <c r="BP1" s="83"/>
-      <c r="BQ1" s="83"/>
-      <c r="BR1" s="75"/>
+      <c r="BI1" s="87"/>
+      <c r="BJ1" s="87"/>
+      <c r="BK1" s="87"/>
+      <c r="BL1" s="87"/>
+      <c r="BM1" s="87"/>
+      <c r="BN1" s="87"/>
+      <c r="BO1" s="87"/>
+      <c r="BP1" s="87"/>
+      <c r="BQ1" s="87"/>
+      <c r="BR1" s="72"/>
     </row>
     <row r="2" spans="1:70" ht="28" customHeight="1">
       <c r="A2" s="2"/>
@@ -3403,7 +3453,7 @@
       <c r="E5" s="6">
         <v>46275</v>
       </c>
-      <c r="F5" s="87" t="s">
+      <c r="F5" s="68" t="s">
         <v>3</v>
       </c>
       <c r="G5" s="18">
@@ -3489,7 +3539,7 @@
       <c r="E6" s="6">
         <v>46275</v>
       </c>
-      <c r="F6" s="87" t="s">
+      <c r="F6" s="68" t="s">
         <v>3</v>
       </c>
       <c r="G6" s="18">
@@ -3575,7 +3625,7 @@
       <c r="E7" s="6">
         <v>46276</v>
       </c>
-      <c r="F7" s="87" t="s">
+      <c r="F7" s="68" t="s">
         <v>3</v>
       </c>
       <c r="G7" s="18">
@@ -3661,7 +3711,7 @@
       <c r="E8" s="6">
         <v>46277</v>
       </c>
-      <c r="F8" s="87" t="s">
+      <c r="F8" s="68" t="s">
         <v>3</v>
       </c>
       <c r="G8" s="18">
@@ -3747,7 +3797,7 @@
       <c r="E9" s="6">
         <v>46281</v>
       </c>
-      <c r="F9" s="87" t="s">
+      <c r="F9" s="68" t="s">
         <v>3</v>
       </c>
       <c r="G9" s="18">
@@ -3833,7 +3883,7 @@
       <c r="E10" s="6">
         <v>46280</v>
       </c>
-      <c r="F10" s="87" t="s">
+      <c r="F10" s="68" t="s">
         <v>3</v>
       </c>
       <c r="G10" s="18">
@@ -3919,7 +3969,7 @@
       <c r="E11" s="6">
         <v>46283</v>
       </c>
-      <c r="F11" s="87" t="s">
+      <c r="F11" s="68" t="s">
         <v>3</v>
       </c>
       <c r="G11" s="18">
@@ -4077,7 +4127,7 @@
       <c r="BQ12" s="13"/>
       <c r="BR12" s="13"/>
     </row>
-    <row r="13" spans="1:70" ht="26" customHeight="1">
+    <row r="13" spans="1:70" ht="28">
       <c r="A13" s="5" t="s">
         <v>69</v>
       </c>
@@ -4093,7 +4143,7 @@
       <c r="E13" s="6">
         <v>46287</v>
       </c>
-      <c r="F13" s="88" t="s">
+      <c r="F13" s="69" t="s">
         <v>3</v>
       </c>
       <c r="G13" s="18">
@@ -4163,7 +4213,7 @@
       <c r="BQ13" s="4"/>
       <c r="BR13" s="4"/>
     </row>
-    <row r="14" spans="1:70" ht="26" customHeight="1">
+    <row r="14" spans="1:70" ht="28">
       <c r="A14" s="5" t="s">
         <v>71</v>
       </c>
@@ -4179,7 +4229,7 @@
       <c r="E14" s="6">
         <v>46291</v>
       </c>
-      <c r="F14" s="87" t="s">
+      <c r="F14" s="68" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="18">
@@ -4249,7 +4299,7 @@
       <c r="BQ14" s="4"/>
       <c r="BR14" s="4"/>
     </row>
-    <row r="15" spans="1:70" ht="26" customHeight="1">
+    <row r="15" spans="1:70" ht="28">
       <c r="A15" s="5" t="s">
         <v>73</v>
       </c>
@@ -4265,7 +4315,7 @@
       <c r="E15" s="6">
         <v>46294</v>
       </c>
-      <c r="F15" s="87" t="s">
+      <c r="F15" s="68" t="s">
         <v>3</v>
       </c>
       <c r="G15" s="18">
@@ -4335,7 +4385,7 @@
       <c r="BQ15" s="4"/>
       <c r="BR15" s="4"/>
     </row>
-    <row r="16" spans="1:70" ht="26" customHeight="1">
+    <row r="16" spans="1:70" ht="28">
       <c r="A16" s="5" t="s">
         <v>75</v>
       </c>
@@ -4351,7 +4401,7 @@
       <c r="E16" s="6">
         <v>46296</v>
       </c>
-      <c r="F16" s="87" t="s">
+      <c r="F16" s="68" t="s">
         <v>3</v>
       </c>
       <c r="G16" s="18">
@@ -4421,7 +4471,7 @@
       <c r="BQ16" s="4"/>
       <c r="BR16" s="4"/>
     </row>
-    <row r="17" spans="1:70" ht="26" customHeight="1">
+    <row r="17" spans="1:70" ht="28">
       <c r="A17" s="5" t="s">
         <v>77</v>
       </c>
@@ -4437,7 +4487,7 @@
       <c r="E17" s="6">
         <v>46298</v>
       </c>
-      <c r="F17" s="87" t="s">
+      <c r="F17" s="68" t="s">
         <v>3</v>
       </c>
       <c r="G17" s="18">
@@ -4507,7 +4557,7 @@
       <c r="BQ17" s="4"/>
       <c r="BR17" s="4"/>
     </row>
-    <row r="18" spans="1:70" ht="26" customHeight="1">
+    <row r="18" spans="1:70" ht="28">
       <c r="A18" s="5" t="s">
         <v>79</v>
       </c>
@@ -4523,7 +4573,7 @@
       <c r="E18" s="6">
         <v>46302</v>
       </c>
-      <c r="F18" s="87" t="s">
+      <c r="F18" s="68" t="s">
         <v>3</v>
       </c>
       <c r="G18" s="18">
@@ -4593,7 +4643,7 @@
       <c r="BQ18" s="4"/>
       <c r="BR18" s="4"/>
     </row>
-    <row r="19" spans="1:70" ht="38" customHeight="1">
+    <row r="19" spans="1:70" ht="42">
       <c r="A19" s="5" t="s">
         <v>81</v>
       </c>
@@ -4609,7 +4659,7 @@
       <c r="E19" s="6">
         <v>46302</v>
       </c>
-      <c r="F19" s="87" t="s">
+      <c r="F19" s="68" t="s">
         <v>3</v>
       </c>
       <c r="G19" s="18">
@@ -4767,7 +4817,7 @@
       <c r="BQ20" s="13"/>
       <c r="BR20" s="13"/>
     </row>
-    <row r="21" spans="1:70" ht="26" customHeight="1">
+    <row r="21" spans="1:70" ht="28">
       <c r="A21" s="5" t="s">
         <v>86</v>
       </c>
@@ -4783,7 +4833,7 @@
       <c r="E21" s="6">
         <v>46294</v>
       </c>
-      <c r="F21" s="87" t="s">
+      <c r="F21" s="68" t="s">
         <v>3</v>
       </c>
       <c r="G21" s="18">
@@ -4853,7 +4903,7 @@
       <c r="BQ21" s="4"/>
       <c r="BR21" s="4"/>
     </row>
-    <row r="22" spans="1:70" ht="26" customHeight="1">
+    <row r="22" spans="1:70" ht="28">
       <c r="A22" s="5" t="s">
         <v>88</v>
       </c>
@@ -4869,7 +4919,7 @@
       <c r="E22" s="6">
         <v>46297</v>
       </c>
-      <c r="F22" s="87" t="s">
+      <c r="F22" s="68" t="s">
         <v>3</v>
       </c>
       <c r="G22" s="18">
@@ -4939,7 +4989,7 @@
       <c r="BQ22" s="4"/>
       <c r="BR22" s="4"/>
     </row>
-    <row r="23" spans="1:70" ht="26" customHeight="1">
+    <row r="23" spans="1:70" ht="28">
       <c r="A23" s="5" t="s">
         <v>90</v>
       </c>
@@ -4955,7 +5005,7 @@
       <c r="E23" s="6">
         <v>46299</v>
       </c>
-      <c r="F23" s="87" t="s">
+      <c r="F23" s="68" t="s">
         <v>3</v>
       </c>
       <c r="G23" s="18">
@@ -5025,7 +5075,7 @@
       <c r="BQ23" s="4"/>
       <c r="BR23" s="4"/>
     </row>
-    <row r="24" spans="1:70" ht="26" customHeight="1">
+    <row r="24" spans="1:70" ht="28">
       <c r="A24" s="5" t="s">
         <v>92</v>
       </c>
@@ -5041,7 +5091,7 @@
       <c r="E24" s="6">
         <v>46301</v>
       </c>
-      <c r="F24" s="87" t="s">
+      <c r="F24" s="68" t="s">
         <v>3</v>
       </c>
       <c r="G24" s="18">
@@ -5111,7 +5161,7 @@
       <c r="BQ24" s="4"/>
       <c r="BR24" s="4"/>
     </row>
-    <row r="25" spans="1:70" ht="26" customHeight="1">
+    <row r="25" spans="1:70" ht="28">
       <c r="A25" s="5" t="s">
         <v>94</v>
       </c>
@@ -5127,7 +5177,7 @@
       <c r="E25" s="6">
         <v>46302</v>
       </c>
-      <c r="F25" s="87" t="s">
+      <c r="F25" s="68" t="s">
         <v>3</v>
       </c>
       <c r="G25" s="18">
@@ -5215,11 +5265,11 @@
       </c>
       <c r="F26" s="20" t="str">
         <f>IF(G26=1,"Đã hoàn thành",IF(G26=0,"Chưa thực hiện","Đang thực hiện"))</f>
-        <v>Chưa thực hiện</v>
+        <v>Đã hoàn thành</v>
       </c>
       <c r="G26" s="23">
         <f>AVERAGE(G27)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="21"/>
       <c r="I26" s="21"/>
@@ -5303,11 +5353,11 @@
       </c>
       <c r="F27" s="25" t="str">
         <f>IF(G27=1,"Đã hoàn thành",IF(G27=0,"Chưa thực hiện","Đang thực hiện"))</f>
-        <v>Chưa thực hiện</v>
+        <v>Đã hoàn thành</v>
       </c>
       <c r="G27" s="28">
         <f>AVERAGE(G28,G29,G30,G31,G32,G33,G34,G35)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="26"/>
       <c r="I27" s="26"/>
@@ -5373,7 +5423,7 @@
       <c r="BQ27" s="26"/>
       <c r="BR27" s="26"/>
     </row>
-    <row r="28" spans="1:70" ht="26" customHeight="1">
+    <row r="28" spans="1:70" ht="28">
       <c r="A28" s="5" t="s">
         <v>101</v>
       </c>
@@ -5389,11 +5439,11 @@
       <c r="E28" s="6">
         <v>46305</v>
       </c>
-      <c r="F28" s="19" t="s">
-        <v>5</v>
+      <c r="F28" s="70" t="s">
+        <v>3</v>
       </c>
       <c r="G28" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
@@ -5459,7 +5509,7 @@
       <c r="BQ28" s="4"/>
       <c r="BR28" s="4"/>
     </row>
-    <row r="29" spans="1:70" ht="26" customHeight="1">
+    <row r="29" spans="1:70" ht="28">
       <c r="A29" s="5" t="s">
         <v>103</v>
       </c>
@@ -5475,11 +5525,11 @@
       <c r="E29" s="6">
         <v>46309</v>
       </c>
-      <c r="F29" s="19" t="s">
-        <v>5</v>
+      <c r="F29" s="70" t="s">
+        <v>3</v>
       </c>
       <c r="G29" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
@@ -5545,7 +5595,7 @@
       <c r="BQ29" s="4"/>
       <c r="BR29" s="4"/>
     </row>
-    <row r="30" spans="1:70" ht="26" customHeight="1">
+    <row r="30" spans="1:70" ht="28">
       <c r="A30" s="5" t="s">
         <v>105</v>
       </c>
@@ -5561,11 +5611,11 @@
       <c r="E30" s="6">
         <v>46311</v>
       </c>
-      <c r="F30" s="19" t="s">
-        <v>5</v>
+      <c r="F30" s="70" t="s">
+        <v>3</v>
       </c>
       <c r="G30" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
@@ -5631,7 +5681,7 @@
       <c r="BQ30" s="4"/>
       <c r="BR30" s="4"/>
     </row>
-    <row r="31" spans="1:70" ht="26" customHeight="1">
+    <row r="31" spans="1:70" ht="28">
       <c r="A31" s="5" t="s">
         <v>107</v>
       </c>
@@ -5647,11 +5697,11 @@
       <c r="E31" s="6">
         <v>46313</v>
       </c>
-      <c r="F31" s="19" t="s">
-        <v>5</v>
+      <c r="F31" s="70" t="s">
+        <v>3</v>
       </c>
       <c r="G31" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
@@ -5717,7 +5767,7 @@
       <c r="BQ31" s="4"/>
       <c r="BR31" s="4"/>
     </row>
-    <row r="32" spans="1:70" ht="26" customHeight="1">
+    <row r="32" spans="1:70" ht="28">
       <c r="A32" s="5" t="s">
         <v>109</v>
       </c>
@@ -5733,11 +5783,11 @@
       <c r="E32" s="6">
         <v>46314</v>
       </c>
-      <c r="F32" s="19" t="s">
-        <v>5</v>
+      <c r="F32" s="70" t="s">
+        <v>3</v>
       </c>
       <c r="G32" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -5803,7 +5853,7 @@
       <c r="BQ32" s="4"/>
       <c r="BR32" s="4"/>
     </row>
-    <row r="33" spans="1:70" ht="26" customHeight="1">
+    <row r="33" spans="1:70" ht="28">
       <c r="A33" s="5" t="s">
         <v>111</v>
       </c>
@@ -5819,11 +5869,11 @@
       <c r="E33" s="6">
         <v>46316</v>
       </c>
-      <c r="F33" s="19" t="s">
-        <v>5</v>
+      <c r="F33" s="70" t="s">
+        <v>3</v>
       </c>
       <c r="G33" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
@@ -5889,7 +5939,7 @@
       <c r="BQ33" s="4"/>
       <c r="BR33" s="4"/>
     </row>
-    <row r="34" spans="1:70" ht="26" customHeight="1">
+    <row r="34" spans="1:70" ht="28">
       <c r="A34" s="5" t="s">
         <v>113</v>
       </c>
@@ -5905,11 +5955,11 @@
       <c r="E34" s="6">
         <v>46318</v>
       </c>
-      <c r="F34" s="19" t="s">
-        <v>5</v>
+      <c r="F34" s="70" t="s">
+        <v>3</v>
       </c>
       <c r="G34" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
@@ -5975,7 +6025,7 @@
       <c r="BQ34" s="4"/>
       <c r="BR34" s="4"/>
     </row>
-    <row r="35" spans="1:70" ht="26" customHeight="1">
+    <row r="35" spans="1:70" ht="28">
       <c r="A35" s="5" t="s">
         <v>115</v>
       </c>
@@ -5991,11 +6041,11 @@
       <c r="E35" s="6">
         <v>46319</v>
       </c>
-      <c r="F35" s="19" t="s">
-        <v>5</v>
+      <c r="F35" s="70" t="s">
+        <v>3</v>
       </c>
       <c r="G35" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
@@ -6237,7 +6287,7 @@
       <c r="BQ37" s="37"/>
       <c r="BR37" s="37"/>
     </row>
-    <row r="38" spans="1:70" ht="26" customHeight="1">
+    <row r="38" spans="1:70" ht="28">
       <c r="A38" s="5" t="s">
         <v>122</v>
       </c>
@@ -6323,7 +6373,7 @@
       <c r="BQ38" s="4"/>
       <c r="BR38" s="4"/>
     </row>
-    <row r="39" spans="1:70" ht="26" customHeight="1">
+    <row r="39" spans="1:70" ht="28">
       <c r="A39" s="5" t="s">
         <v>124</v>
       </c>
@@ -6409,7 +6459,7 @@
       <c r="BQ39" s="4"/>
       <c r="BR39" s="4"/>
     </row>
-    <row r="40" spans="1:70" ht="26" customHeight="1">
+    <row r="40" spans="1:70" ht="28">
       <c r="A40" s="5" t="s">
         <v>126</v>
       </c>
@@ -6583,7 +6633,7 @@
       <c r="BQ41" s="37"/>
       <c r="BR41" s="37"/>
     </row>
-    <row r="42" spans="1:70" ht="26" customHeight="1">
+    <row r="42" spans="1:70" ht="28">
       <c r="A42" s="5" t="s">
         <v>130</v>
       </c>
@@ -6669,7 +6719,7 @@
       <c r="BQ42" s="4"/>
       <c r="BR42" s="4"/>
     </row>
-    <row r="43" spans="1:70" ht="26" customHeight="1">
+    <row r="43" spans="1:70" ht="28">
       <c r="A43" s="5" t="s">
         <v>132</v>
       </c>
@@ -6755,7 +6805,7 @@
       <c r="BQ43" s="4"/>
       <c r="BR43" s="4"/>
     </row>
-    <row r="44" spans="1:70" ht="26" customHeight="1">
+    <row r="44" spans="1:70" ht="28">
       <c r="A44" s="5" t="s">
         <v>134</v>
       </c>
@@ -7275,7 +7325,7 @@
       <c r="BQ49" s="40"/>
       <c r="BR49" s="40"/>
     </row>
-    <row r="50" spans="1:70" ht="26" customHeight="1">
+    <row r="50" spans="1:70" ht="28">
       <c r="A50" s="5" t="s">
         <v>146</v>
       </c>
@@ -7361,7 +7411,7 @@
       <c r="BQ50" s="4"/>
       <c r="BR50" s="4"/>
     </row>
-    <row r="51" spans="1:70" ht="26" customHeight="1">
+    <row r="51" spans="1:70">
       <c r="A51" s="5" t="s">
         <v>148</v>
       </c>
@@ -7447,7 +7497,7 @@
       <c r="BQ51" s="4"/>
       <c r="BR51" s="4"/>
     </row>
-    <row r="52" spans="1:70" ht="26" customHeight="1">
+    <row r="52" spans="1:70" ht="28">
       <c r="A52" s="5" t="s">
         <v>150</v>
       </c>
@@ -7533,7 +7583,7 @@
       <c r="BQ52" s="41"/>
       <c r="BR52" s="4"/>
     </row>
-    <row r="53" spans="1:70" ht="26" customHeight="1">
+    <row r="53" spans="1:70" ht="28">
       <c r="A53" s="5" t="s">
         <v>152</v>
       </c>
@@ -7619,7 +7669,7 @@
       <c r="BQ53" s="41"/>
       <c r="BR53" s="4"/>
     </row>
-    <row r="54" spans="1:70" ht="26" customHeight="1">
+    <row r="54" spans="1:70" ht="28">
       <c r="A54" s="5" t="s">
         <v>154</v>
       </c>
@@ -7793,7 +7843,7 @@
       <c r="BQ55" s="40"/>
       <c r="BR55" s="40"/>
     </row>
-    <row r="56" spans="1:70" ht="26" customHeight="1">
+    <row r="56" spans="1:70" ht="28">
       <c r="A56" s="5" t="s">
         <v>159</v>
       </c>
@@ -7879,7 +7929,7 @@
       <c r="BQ56" s="4"/>
       <c r="BR56" s="4"/>
     </row>
-    <row r="57" spans="1:70" ht="26" customHeight="1">
+    <row r="57" spans="1:70" ht="28">
       <c r="A57" s="5" t="s">
         <v>161</v>
       </c>
@@ -7965,7 +8015,7 @@
       <c r="BQ57" s="41"/>
       <c r="BR57" s="41"/>
     </row>
-    <row r="58" spans="1:70" ht="26" customHeight="1">
+    <row r="58" spans="1:70" ht="28">
       <c r="A58" s="5" t="s">
         <v>163</v>
       </c>
@@ -8085,25 +8135,25 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="38" customWidth="1"/>
-    <col min="4" max="4" width="62" customWidth="1"/>
+    <col min="1" max="1" width="8" style="67" customWidth="1"/>
+    <col min="2" max="2" width="22" style="67" customWidth="1"/>
+    <col min="3" max="3" width="38" style="67" customWidth="1"/>
+    <col min="4" max="4" width="62" style="67" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="79" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
     </row>
     <row r="2" spans="1:4" ht="14.5" customHeight="1">
-      <c r="A2" s="86"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
+      <c r="A2" s="90"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="64" t="s">
@@ -8147,7 +8197,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="30" customHeight="1">
+    <row r="6" spans="1:4" ht="42">
       <c r="A6" s="65">
         <v>3</v>
       </c>
@@ -8378,31 +8428,31 @@
   <dimension ref="A1:F69"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="36" customWidth="1"/>
+    <col min="1" max="1" width="23" style="67" customWidth="1"/>
+    <col min="2" max="2" width="29" style="67" customWidth="1"/>
+    <col min="3" max="3" width="42" style="67" customWidth="1"/>
+    <col min="4" max="4" width="14" style="67" customWidth="1"/>
+    <col min="5" max="5" width="20" style="67" customWidth="1"/>
+    <col min="6" max="6" width="36" style="67" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="79" t="s">
         <v>220</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
     </row>
     <row r="2" spans="1:6" ht="14.5" customHeight="1">
-      <c r="A2" s="86"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
+      <c r="A2" s="90"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="64" t="s">
@@ -8778,37 +8828,41 @@
         <v>101</v>
       </c>
       <c r="E21" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F21" s="66" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="22" spans="1:6" ht="23" customHeight="1">
       <c r="A22" s="66" t="s">
         <v>276</v>
       </c>
       <c r="B22" s="66" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C22" s="66" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D22" s="65" t="s">
         <v>101</v>
       </c>
       <c r="E22" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F22" s="66" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="23" spans="1:6" ht="23" customHeight="1">
       <c r="A23" s="66" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B23" s="66" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C23" s="66" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D23" s="65" t="s">
         <v>86</v>
@@ -8817,18 +8871,18 @@
         <v>3</v>
       </c>
       <c r="F23" s="66" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="23" customHeight="1">
       <c r="A24" s="66" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B24" s="66" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C24" s="66" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D24" s="65" t="s">
         <v>86</v>
@@ -8837,18 +8891,18 @@
         <v>3</v>
       </c>
       <c r="F24" s="66" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="23" customHeight="1">
       <c r="A25" s="66" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B25" s="66" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C25" s="66" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D25" s="65" t="s">
         <v>86</v>
@@ -8857,18 +8911,18 @@
         <v>3</v>
       </c>
       <c r="F25" s="66" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="23" customHeight="1">
       <c r="A26" s="66" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B26" s="66" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C26" s="66" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D26" s="65" t="s">
         <v>88</v>
@@ -8877,18 +8931,18 @@
         <v>3</v>
       </c>
       <c r="F26" s="66" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="23" customHeight="1">
       <c r="A27" s="66" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B27" s="66" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C27" s="66" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D27" s="65" t="s">
         <v>88</v>
@@ -8897,18 +8951,18 @@
         <v>3</v>
       </c>
       <c r="F27" s="66" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="23" customHeight="1">
       <c r="A28" s="66" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C28" s="66" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D28" s="65" t="s">
         <v>88</v>
@@ -8917,18 +8971,18 @@
         <v>3</v>
       </c>
       <c r="F28" s="66" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="23" customHeight="1">
       <c r="A29" s="66" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B29" s="66" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C29" s="66" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D29" s="65" t="s">
         <v>90</v>
@@ -8937,162 +8991,178 @@
         <v>3</v>
       </c>
       <c r="F29" s="66" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="23" customHeight="1">
       <c r="A30" s="66" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B30" s="66" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C30" s="66" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D30" s="65" t="s">
         <v>103</v>
       </c>
       <c r="E30" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F30" s="66" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="23" customHeight="1">
       <c r="A31" s="66" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B31" s="66" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C31" s="66" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D31" s="65" t="s">
         <v>103</v>
       </c>
       <c r="E31" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F31" s="66" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="32" spans="1:6" ht="23" customHeight="1">
       <c r="A32" s="66" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B32" s="66" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C32" s="66" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D32" s="65" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E32" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F32" s="66" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="33" spans="1:6" ht="23" customHeight="1">
       <c r="A33" s="66" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B33" s="66" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C33" s="66" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D33" s="65" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E33" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F33" s="66" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="34" spans="1:6" ht="23" customHeight="1">
       <c r="A34" s="66" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B34" s="66" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C34" s="66" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D34" s="65" t="s">
         <v>107</v>
       </c>
       <c r="E34" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F34" s="66" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="35" spans="1:6" ht="23" customHeight="1">
       <c r="A35" s="66" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B35" s="66" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C35" s="66" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="D35" s="65" t="s">
         <v>107</v>
       </c>
       <c r="E35" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F35" s="66" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="36" spans="1:6" ht="23" customHeight="1">
       <c r="A36" s="66" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B36" s="66" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C36" s="66" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="D36" s="65" t="s">
         <v>107</v>
       </c>
       <c r="E36" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F36" s="66" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="37" spans="1:6" ht="23" customHeight="1">
       <c r="A37" s="66" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B37" s="66" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C37" s="66" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="D37" s="65" t="s">
         <v>109</v>
       </c>
       <c r="E37" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F37" s="66" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="38" spans="1:6" ht="23" customHeight="1">
       <c r="A38" s="66" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B38" s="66" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C38" s="66" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D38" s="65" t="s">
         <v>77</v>
@@ -9101,18 +9171,18 @@
         <v>3</v>
       </c>
       <c r="F38" s="66" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="23" customHeight="1">
       <c r="A39" s="66" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B39" s="66" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C39" s="66" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D39" s="65" t="s">
         <v>77</v>
@@ -9121,54 +9191,58 @@
         <v>3</v>
       </c>
       <c r="F39" s="66" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="23" customHeight="1">
       <c r="A40" s="66" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B40" s="66" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="C40" s="66" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="D40" s="65" t="s">
         <v>111</v>
       </c>
       <c r="E40" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F40" s="66" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="41" spans="1:6" ht="23" customHeight="1">
       <c r="A41" s="66" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B41" s="66" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="C41" s="66" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="D41" s="65" t="s">
         <v>111</v>
       </c>
       <c r="E41" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F41" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F41" s="66" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="42" spans="1:6" ht="23" customHeight="1">
       <c r="A42" s="66" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B42" s="66" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C42" s="66" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D42" s="65" t="s">
         <v>77</v>
@@ -9177,18 +9251,18 @@
         <v>3</v>
       </c>
       <c r="F42" s="66" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="23" customHeight="1">
       <c r="A43" s="66" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B43" s="66" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="C43" s="66" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="D43" s="65" t="s">
         <v>77</v>
@@ -9197,290 +9271,318 @@
         <v>3</v>
       </c>
       <c r="F43" s="66" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="23" customHeight="1">
       <c r="A44" s="66" t="s">
+        <v>340</v>
+      </c>
+      <c r="B44" s="66" t="s">
+        <v>341</v>
+      </c>
+      <c r="C44" s="66" t="s">
+        <v>342</v>
+      </c>
+      <c r="D44" s="65" t="s">
+        <v>343</v>
+      </c>
+      <c r="E44" s="65" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="66" t="s">
         <v>333</v>
       </c>
-      <c r="B44" s="66" t="s">
-        <v>334</v>
-      </c>
-      <c r="C44" s="66" t="s">
-        <v>335</v>
-      </c>
-      <c r="D44" s="65" t="s">
-        <v>336</v>
-      </c>
-      <c r="E44" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" s="66"/>
     </row>
     <row r="45" spans="1:6" ht="23" customHeight="1">
       <c r="A45" s="66" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B45" s="66" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C45" s="66" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="D45" s="65" t="s">
         <v>111</v>
       </c>
       <c r="E45" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F45" s="66" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="46" spans="1:6" ht="23" customHeight="1">
       <c r="A46" s="66" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B46" s="66" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C46" s="66" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="D46" s="65" t="s">
         <v>111</v>
       </c>
       <c r="E46" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F46" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F46" s="66" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="47" spans="1:6" ht="23" customHeight="1">
       <c r="A47" s="66" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B47" s="66" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C47" s="66" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="D47" s="65" t="s">
         <v>111</v>
       </c>
       <c r="E47" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F47" s="66" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="48" spans="1:6" ht="23" customHeight="1">
       <c r="A48" s="66" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B48" s="66" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C48" s="66" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="D48" s="65" t="s">
         <v>111</v>
       </c>
       <c r="E48" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F48" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F48" s="66" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="49" spans="1:6" ht="23" customHeight="1">
       <c r="A49" s="66" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B49" s="66" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="C49" s="66" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="D49" s="65" t="s">
         <v>111</v>
       </c>
       <c r="E49" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F49" s="66" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="50" spans="1:6" ht="23" customHeight="1">
       <c r="A50" s="66" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B50" s="66" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="C50" s="66" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="D50" s="65" t="s">
         <v>113</v>
       </c>
       <c r="E50" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F50" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F50" s="66" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="51" spans="1:6" ht="23" customHeight="1">
       <c r="A51" s="66" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B51" s="66" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C51" s="66" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="D51" s="65" t="s">
         <v>113</v>
       </c>
       <c r="E51" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F51" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F51" s="66" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="52" spans="1:6" ht="23" customHeight="1">
       <c r="A52" s="66" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B52" s="66" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="C52" s="66" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="D52" s="65" t="s">
         <v>113</v>
       </c>
       <c r="E52" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F52" s="66" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="53" spans="1:6" ht="23" customHeight="1">
       <c r="A53" s="66" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B53" s="66" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C53" s="66" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="D53" s="65" t="s">
         <v>113</v>
       </c>
       <c r="E53" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F53" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F53" s="66" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="54" spans="1:6" ht="23" customHeight="1">
       <c r="A54" s="66" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B54" s="66" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C54" s="66" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="D54" s="65" t="s">
         <v>115</v>
       </c>
       <c r="E54" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F54" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F54" s="66" t="s">
+        <v>369</v>
+      </c>
     </row>
     <row r="55" spans="1:6" ht="23" customHeight="1">
       <c r="A55" s="66" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B55" s="66" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="C55" s="66" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="D55" s="65" t="s">
         <v>115</v>
       </c>
       <c r="E55" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F55" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F55" s="66" t="s">
+        <v>369</v>
+      </c>
     </row>
     <row r="56" spans="1:6" ht="23" customHeight="1">
       <c r="A56" s="66" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B56" s="66" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="C56" s="66" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D56" s="65" t="s">
         <v>115</v>
       </c>
       <c r="E56" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F56" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F56" s="66" t="s">
+        <v>369</v>
+      </c>
     </row>
     <row r="57" spans="1:6" ht="23" customHeight="1">
       <c r="A57" s="66" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B57" s="66" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="C57" s="66" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="D57" s="65" t="s">
         <v>115</v>
       </c>
       <c r="E57" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F57" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F57" s="66" t="s">
+        <v>369</v>
+      </c>
     </row>
     <row r="58" spans="1:6" ht="23" customHeight="1">
       <c r="A58" s="66" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="B58" s="66" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="C58" s="66" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="D58" s="65" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="E58" s="65" t="s">
         <v>4</v>
       </c>
       <c r="F58" s="66" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="23" customHeight="1">
       <c r="A59" s="66" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="B59" s="66" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="C59" s="66" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="D59" s="65" t="s">
         <v>56</v>
@@ -9489,18 +9591,18 @@
         <v>3</v>
       </c>
       <c r="F59" s="66" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="23" customHeight="1">
       <c r="A60" s="66" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="B60" s="66" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="C60" s="66" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="D60" s="65" t="s">
         <v>59</v>
@@ -9509,18 +9611,18 @@
         <v>3</v>
       </c>
       <c r="F60" s="66" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="23" customHeight="1">
       <c r="A61" s="66" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="B61" s="66" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="C61" s="66" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="D61" s="65" t="s">
         <v>59</v>
@@ -9529,18 +9631,18 @@
         <v>3</v>
       </c>
       <c r="F61" s="66" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="23" customHeight="1">
       <c r="A62" s="66" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="B62" s="66" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="C62" s="66" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="D62" s="65" t="s">
         <v>56</v>
@@ -9549,18 +9651,18 @@
         <v>3</v>
       </c>
       <c r="F62" s="66" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="23" customHeight="1">
       <c r="A63" s="66" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B63" s="66" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="C63" s="66" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="D63" s="65" t="s">
         <v>122</v>
@@ -9572,13 +9674,13 @@
     </row>
     <row r="64" spans="1:6" ht="23" customHeight="1">
       <c r="A64" s="66" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B64" s="66" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="C64" s="66" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="D64" s="65" t="s">
         <v>124</v>
@@ -9590,13 +9692,13 @@
     </row>
     <row r="65" spans="1:6" ht="23" customHeight="1">
       <c r="A65" s="66" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B65" s="66" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="C65" s="66" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="D65" s="65" t="s">
         <v>126</v>
@@ -9608,33 +9710,33 @@
     </row>
     <row r="66" spans="1:6" ht="23" customHeight="1">
       <c r="A66" s="66" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B66" s="66" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="C66" s="66" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="D66" s="65" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="E66" s="65" t="s">
         <v>3</v>
       </c>
       <c r="F66" s="66" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="23" customHeight="1">
       <c r="A67" s="66" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B67" s="66" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="C67" s="66" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D67" s="65" t="s">
         <v>75</v>
@@ -9643,36 +9745,38 @@
         <v>3</v>
       </c>
       <c r="F67" s="66" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="23" customHeight="1">
       <c r="A68" s="66" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B68" s="66" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="C68" s="66" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="D68" s="65" t="s">
         <v>103</v>
       </c>
       <c r="E68" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F68" s="66"/>
+        <v>3</v>
+      </c>
+      <c r="F68" s="66" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="69" spans="1:6" ht="23" customHeight="1">
       <c r="A69" s="66" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="B69" s="66" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="C69" s="66" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="D69" s="65" t="s">
         <v>134</v>
@@ -9704,61 +9808,61 @@
   <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="47" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="43" customWidth="1"/>
+    <col min="1" max="1" width="20" style="67" customWidth="1"/>
+    <col min="2" max="2" width="47" style="67" customWidth="1"/>
+    <col min="3" max="3" width="19" style="67" customWidth="1"/>
+    <col min="4" max="4" width="25" style="67" customWidth="1"/>
+    <col min="5" max="5" width="43" style="67" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="73" t="s">
-        <v>401</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
+      <c r="A1" s="79" t="s">
+        <v>410</v>
+      </c>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
     </row>
     <row r="2" spans="1:5" ht="14.5" customHeight="1">
-      <c r="A2" s="86"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
+      <c r="A2" s="90"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
     </row>
     <row r="3" spans="1:5" ht="28" customHeight="1">
       <c r="A3" s="64" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="B3" s="64" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="C3" s="64" t="s">
         <v>224</v>
       </c>
       <c r="D3" s="64" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="E3" s="64" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="34" customHeight="1">
       <c r="A4" s="66" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="B4" s="66" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="C4" s="65" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="D4" s="65" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="34" customHeight="1">
@@ -9766,254 +9870,254 @@
         <v>181</v>
       </c>
       <c r="B5" s="66" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="D5" s="65" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="E5" s="66" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="34" customHeight="1">
       <c r="A6" s="66" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="B6" s="66" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="D6" s="65" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="E6" s="66" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="34" customHeight="1">
       <c r="A7" s="66" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="B7" s="66" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="C7" s="65" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="D7" s="65" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="E7" s="66" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="34" customHeight="1">
       <c r="A8" s="66" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="B8" s="66" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="C8" s="65" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="D8" s="65" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="E8" s="66" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="34" customHeight="1">
       <c r="A9" s="66" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="B9" s="66" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="C9" s="65" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="D9" s="65" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="E9" s="66" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="34" customHeight="1">
       <c r="A10" s="66" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="C10" s="65" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="D10" s="65" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="E10" s="66" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="34" customHeight="1">
       <c r="A11" s="66" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="B11" s="66" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="C11" s="65" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="D11" s="65" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="E11" s="66" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="34" customHeight="1">
       <c r="A12" s="66" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="B12" s="66" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="C12" s="65" t="s">
         <v>150</v>
       </c>
       <c r="D12" s="65" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="E12" s="66" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="34" customHeight="1">
       <c r="A13" s="66" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="B13" s="66" t="s">
+        <v>452</v>
+      </c>
+      <c r="C13" s="65" t="s">
+        <v>453</v>
+      </c>
+      <c r="D13" s="65" t="s">
         <v>443</v>
       </c>
-      <c r="C13" s="65" t="s">
-        <v>444</v>
-      </c>
-      <c r="D13" s="65" t="s">
-        <v>434</v>
-      </c>
       <c r="E13" s="66" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="34" customHeight="1">
       <c r="A14" s="66" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="B14" s="66" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="C14" s="65" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="D14" s="65" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="E14" s="66" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="34" customHeight="1">
       <c r="A15" s="66" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="B15" s="66" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="C15" s="65" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="D15" s="65" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="E15" s="66" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="34" customHeight="1">
       <c r="A16" s="66" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="B16" s="66" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="C16" s="65" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="D16" s="65" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="E16" s="66" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="34" customHeight="1">
       <c r="A17" s="66" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="B17" s="66" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="C17" s="65" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="D17" s="65" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="E17" s="66" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="34" customHeight="1">
       <c r="A18" s="66" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="B18" s="66" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C18" s="65" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="D18" s="65" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="E18" s="66" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="34" customHeight="1">
       <c r="A19" s="66" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="B19" s="66" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="C19" s="65" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="D19" s="65" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="E19" s="66" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
